--- a/result/2D_simulation_result.xlsx
+++ b/result/2D_simulation_result.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c01c344c4fe18c6f/문서/GitHub/Deepkriging_self/result/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{4629B4FD-6946-4CA4-B7D4-3A59B2FAD43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1B6F2FC0-B8AB-4346-BF70-94D25E906031}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{4629B4FD-6946-4CA4-B7D4-3A59B2FAD43D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{720BEF80-1740-4836-8085-F5D202A956C8}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-15225" windowWidth="21840" windowHeight="37920" xr2:uid="{304E559C-9CD2-441E-8304-CC31CBBB22C1}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="88">
   <si>
     <t>Data</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -298,12 +298,6 @@
   <si>
     <t>1. Data Sparsity에 따른 성능 차이 확인
 2. Nugget size에 따른 성능 차이 확인</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1. Basis level에 따른 성능 차이 확인
-2. NN layer 깊이에 따른 성능 차이 확인
-※ Ref. Result : S1_O6</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -513,13 +507,57 @@
     <t>/S3_results</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>W37</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>S6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>/S4_results</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>/S5_results</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>/S6_results</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. Basis level에 따른 성능 및 시간 차이 확인
+2. NN layer 깊이에 따른 성능 및 시간 차이 확인
+※ Ref. Result : S1_O6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.5*var</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Basis level 및 NN layer 깊이 상향에 따른 성능 개선 없음
+2. Basis level이 높을수록, NN layer가 깊을수록 시간 늘어나지만 큰 차이는 아님
+</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="179" formatCode="0.000000"/>
+    <numFmt numFmtId="176" formatCode="0.000000"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -677,35 +715,8 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -716,7 +727,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1033,159 +1071,265 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C13F32D2-7988-44DE-AF43-628B5EA428D7}">
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AL40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="20" width="11" customWidth="1"/>
+    <col min="3" max="38" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="11"/>
-      <c r="S1" s="11"/>
-      <c r="T1" s="11"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
+      <c r="M1" s="9"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
+      <c r="S1" s="9"/>
+      <c r="T1" s="9"/>
+      <c r="U1" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="V1" s="9"/>
+      <c r="W1" s="9"/>
+      <c r="X1" s="9"/>
+      <c r="Y1" s="9"/>
+      <c r="Z1" s="9"/>
+      <c r="AA1" s="9"/>
+      <c r="AB1" s="9"/>
+      <c r="AC1" s="9"/>
+      <c r="AD1" s="9"/>
+      <c r="AE1" s="9"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="9"/>
+      <c r="AH1" s="9"/>
+      <c r="AI1" s="9"/>
+      <c r="AJ1" s="9"/>
+      <c r="AK1" s="9"/>
+      <c r="AL1" s="9"/>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A2" s="9"/>
-      <c r="B2" s="7" t="s">
+    <row r="2" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A2" s="16"/>
+      <c r="B2" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-      <c r="O2" s="11" t="s">
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
+      <c r="L2" s="9"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="P2" s="11"/>
-      <c r="Q2" s="11"/>
-      <c r="R2" s="11"/>
-      <c r="S2" s="11"/>
-      <c r="T2" s="11"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
+      <c r="AA2" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="AB2" s="9"/>
+      <c r="AC2" s="9"/>
+      <c r="AD2" s="9"/>
+      <c r="AE2" s="9"/>
+      <c r="AF2" s="9"/>
+      <c r="AG2" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AH2" s="9"/>
+      <c r="AI2" s="9"/>
+      <c r="AJ2" s="9"/>
+      <c r="AK2" s="9"/>
+      <c r="AL2" s="9"/>
     </row>
-    <row r="3" spans="1:20" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9"/>
-      <c r="B3" s="7" t="s">
+    <row r="3" spans="1:38" ht="65.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="16"/>
+      <c r="B3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-      <c r="L3" s="13"/>
-      <c r="M3" s="13"/>
-      <c r="N3" s="13"/>
-      <c r="O3" s="13" t="s">
+      <c r="D3" s="10"/>
+      <c r="E3" s="10"/>
+      <c r="F3" s="10"/>
+      <c r="G3" s="10"/>
+      <c r="H3" s="10"/>
+      <c r="I3" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="J3" s="10"/>
+      <c r="K3" s="10"/>
+      <c r="L3" s="10"/>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="P3" s="13"/>
-      <c r="Q3" s="13"/>
-      <c r="R3" s="13"/>
-      <c r="S3" s="13"/>
-      <c r="T3" s="13"/>
+      <c r="P3" s="10"/>
+      <c r="Q3" s="10"/>
+      <c r="R3" s="10"/>
+      <c r="S3" s="10"/>
+      <c r="T3" s="10"/>
+      <c r="U3" s="10"/>
+      <c r="V3" s="10"/>
+      <c r="W3" s="10"/>
+      <c r="X3" s="10"/>
+      <c r="Y3" s="10"/>
+      <c r="Z3" s="10"/>
+      <c r="AA3" s="10"/>
+      <c r="AB3" s="10"/>
+      <c r="AC3" s="10"/>
+      <c r="AD3" s="10"/>
+      <c r="AE3" s="10"/>
+      <c r="AF3" s="10"/>
+      <c r="AG3" s="10"/>
+      <c r="AH3" s="10"/>
+      <c r="AI3" s="10"/>
+      <c r="AJ3" s="10"/>
+      <c r="AK3" s="10"/>
+      <c r="AL3" s="10"/>
     </row>
-    <row r="4" spans="1:20" ht="126" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="9"/>
-      <c r="B4" s="7" t="s">
+    <row r="4" spans="1:38" ht="126" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="16"/>
+      <c r="B4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+      <c r="Q4" s="10"/>
+      <c r="R4" s="10"/>
+      <c r="S4" s="10"/>
+      <c r="T4" s="10"/>
+      <c r="U4" s="10"/>
+      <c r="V4" s="10"/>
+      <c r="W4" s="10"/>
+      <c r="X4" s="10"/>
+      <c r="Y4" s="10"/>
+      <c r="Z4" s="10"/>
+      <c r="AA4" s="10"/>
+      <c r="AB4" s="10"/>
+      <c r="AC4" s="10"/>
+      <c r="AD4" s="10"/>
+      <c r="AE4" s="10"/>
+      <c r="AF4" s="10"/>
+      <c r="AG4" s="10"/>
+      <c r="AH4" s="10"/>
+      <c r="AI4" s="10"/>
+      <c r="AJ4" s="10"/>
+      <c r="AK4" s="10"/>
+      <c r="AL4" s="10"/>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A5" s="17"/>
+      <c r="B5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="C5" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-      <c r="N4" s="13"/>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13"/>
-      <c r="Q4" s="13"/>
-      <c r="R4" s="13"/>
-      <c r="S4" s="13"/>
-      <c r="T4" s="13"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="J5" s="11"/>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
+      <c r="N5" s="11"/>
+      <c r="O5" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="P5" s="11"/>
+      <c r="Q5" s="11"/>
+      <c r="R5" s="11"/>
+      <c r="S5" s="11"/>
+      <c r="T5" s="11"/>
+      <c r="U5" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="V5" s="11"/>
+      <c r="W5" s="11"/>
+      <c r="X5" s="11"/>
+      <c r="Y5" s="11"/>
+      <c r="Z5" s="11"/>
+      <c r="AA5" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="11"/>
+      <c r="AD5" s="11"/>
+      <c r="AE5" s="11"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AH5" s="11"/>
+      <c r="AI5" s="11"/>
+      <c r="AJ5" s="11"/>
+      <c r="AK5" s="11"/>
+      <c r="AL5" s="11"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A5" s="10"/>
-      <c r="B5" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1246,9 +1390,63 @@
       <c r="T6" s="3" t="s">
         <v>66</v>
       </c>
+      <c r="U6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="V6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="W6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="X6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AA6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AB6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AD6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AF6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="AG6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AH6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="AJ6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AK6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="AL6" s="3" t="s">
+        <v>66</v>
+      </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
         <v>24</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1290,15 +1488,45 @@
       <c r="N7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
+      <c r="O7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="U7" s="1"/>
+      <c r="V7" s="1"/>
+      <c r="W7" s="1"/>
+      <c r="X7" s="1"/>
+      <c r="Y7" s="1"/>
+      <c r="Z7" s="1"/>
+      <c r="AA7" s="1"/>
+      <c r="AB7" s="1"/>
+      <c r="AC7" s="1"/>
+      <c r="AD7" s="1"/>
+      <c r="AE7" s="1"/>
+      <c r="AF7" s="1"/>
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A8" s="5"/>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A8" s="13"/>
       <c r="B8" s="3" t="s">
         <v>2</v>
       </c>
@@ -1338,15 +1566,45 @@
       <c r="N8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
+      <c r="O8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="U8" s="1"/>
+      <c r="V8" s="1"/>
+      <c r="W8" s="1"/>
+      <c r="X8" s="1"/>
+      <c r="Y8" s="1"/>
+      <c r="Z8" s="1"/>
+      <c r="AA8" s="1"/>
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="1"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A9" s="6"/>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A9" s="14"/>
       <c r="B9" s="3" t="s">
         <v>1</v>
       </c>
@@ -1386,15 +1644,45 @@
       <c r="N9" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
+      <c r="O9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="P9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="R9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="S9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="T9" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="U9" s="1"/>
+      <c r="V9" s="1"/>
+      <c r="W9" s="1"/>
+      <c r="X9" s="1"/>
+      <c r="Y9" s="1"/>
+      <c r="Z9" s="1"/>
+      <c r="AA9" s="1"/>
+      <c r="AB9" s="1"/>
+      <c r="AC9" s="1"/>
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
         <v>25</v>
       </c>
       <c r="B10" s="3" t="s">
@@ -1418,81 +1706,141 @@
       <c r="H10" s="1">
         <v>30</v>
       </c>
-      <c r="I10" s="16">
+      <c r="I10" s="7">
         <v>30</v>
       </c>
-      <c r="J10" s="16">
+      <c r="J10" s="7">
         <v>30</v>
       </c>
-      <c r="K10" s="16">
+      <c r="K10" s="7">
         <v>30</v>
       </c>
-      <c r="L10" s="16">
+      <c r="L10" s="7">
         <v>30</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="7">
         <v>30</v>
       </c>
-      <c r="N10" s="16">
+      <c r="N10" s="7">
         <v>30</v>
       </c>
-      <c r="O10" s="16"/>
-      <c r="P10" s="16"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
+      <c r="O10" s="6">
+        <v>15</v>
+      </c>
+      <c r="P10" s="6">
+        <v>30</v>
+      </c>
+      <c r="Q10" s="6">
+        <v>60</v>
+      </c>
+      <c r="R10" s="6">
+        <v>15</v>
+      </c>
+      <c r="S10" s="6">
+        <v>30</v>
+      </c>
+      <c r="T10" s="6">
+        <v>60</v>
+      </c>
+      <c r="U10" s="1"/>
+      <c r="V10" s="1"/>
+      <c r="W10" s="1"/>
+      <c r="X10" s="1"/>
+      <c r="Y10" s="1"/>
+      <c r="Z10" s="1"/>
+      <c r="AA10" s="7"/>
+      <c r="AB10" s="7"/>
+      <c r="AC10" s="7"/>
+      <c r="AD10" s="7"/>
+      <c r="AE10" s="7"/>
+      <c r="AF10" s="7"/>
+      <c r="AG10" s="7"/>
+      <c r="AH10" s="7"/>
+      <c r="AI10" s="7"/>
+      <c r="AJ10" s="7"/>
+      <c r="AK10" s="7"/>
+      <c r="AL10" s="7"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A11" s="5"/>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A11" s="13"/>
       <c r="B11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="15" t="s">
+      <c r="C11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="J11" s="16" t="s">
+      <c r="J11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="K11" s="16" t="s">
+      <c r="K11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="16" t="s">
+      <c r="L11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="N11" s="16" t="s">
+      <c r="N11" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="O11" s="16"/>
-      <c r="P11" s="16"/>
-      <c r="Q11" s="16"/>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
+      <c r="O11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="R11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="S11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="T11" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="U11" s="5"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="7"/>
+      <c r="AB11" s="7"/>
+      <c r="AC11" s="7"/>
+      <c r="AD11" s="7"/>
+      <c r="AE11" s="7"/>
+      <c r="AF11" s="7"/>
+      <c r="AG11" s="7"/>
+      <c r="AH11" s="7"/>
+      <c r="AI11" s="7"/>
+      <c r="AJ11" s="7"/>
+      <c r="AK11" s="7"/>
+      <c r="AL11" s="7"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A12" s="6"/>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A12" s="14"/>
       <c r="B12" s="3" t="s">
         <v>4</v>
       </c>
@@ -1514,33 +1862,63 @@
       <c r="H12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I12" s="15">
+      <c r="I12" s="6">
         <v>2</v>
       </c>
-      <c r="J12" s="15">
+      <c r="J12" s="6">
         <v>3</v>
       </c>
-      <c r="K12" s="15">
+      <c r="K12" s="6">
         <v>2</v>
       </c>
-      <c r="L12" s="15">
+      <c r="L12" s="6">
         <v>3</v>
       </c>
-      <c r="M12" s="15">
+      <c r="M12" s="6">
         <v>2</v>
       </c>
-      <c r="N12" s="15">
+      <c r="N12" s="6">
         <v>3</v>
       </c>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="15"/>
-      <c r="T12" s="15"/>
+      <c r="O12" s="7">
+        <v>3</v>
+      </c>
+      <c r="P12" s="7">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="7">
+        <v>3</v>
+      </c>
+      <c r="R12" s="7">
+        <v>3</v>
+      </c>
+      <c r="S12" s="7">
+        <v>3</v>
+      </c>
+      <c r="T12" s="7">
+        <v>3</v>
+      </c>
+      <c r="U12" s="1"/>
+      <c r="V12" s="1"/>
+      <c r="W12" s="1"/>
+      <c r="X12" s="1"/>
+      <c r="Y12" s="1"/>
+      <c r="Z12" s="1"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
+      <c r="AG12" s="6"/>
+      <c r="AH12" s="6"/>
+      <c r="AI12" s="6"/>
+      <c r="AJ12" s="6"/>
+      <c r="AK12" s="6"/>
+      <c r="AL12" s="6"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
         <v>0</v>
       </c>
       <c r="B13" s="3" t="s">
@@ -1564,33 +1942,63 @@
       <c r="H13" s="1">
         <v>0.2</v>
       </c>
-      <c r="I13" s="16">
+      <c r="I13" s="7">
         <v>0.2</v>
       </c>
-      <c r="J13" s="16">
+      <c r="J13" s="7">
         <v>0.2</v>
       </c>
-      <c r="K13" s="16">
+      <c r="K13" s="7">
         <v>0.2</v>
       </c>
-      <c r="L13" s="16">
+      <c r="L13" s="7">
         <v>0.2</v>
       </c>
-      <c r="M13" s="16">
+      <c r="M13" s="7">
         <v>0.2</v>
       </c>
-      <c r="N13" s="16">
+      <c r="N13" s="7">
         <v>0.2</v>
       </c>
-      <c r="O13" s="16"/>
-      <c r="P13" s="16"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
+      <c r="O13" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="P13" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="Q13" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="R13" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="S13" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="T13" s="7">
+        <v>0.2</v>
+      </c>
+      <c r="U13" s="1"/>
+      <c r="V13" s="1"/>
+      <c r="W13" s="1"/>
+      <c r="X13" s="1"/>
+      <c r="Y13" s="1"/>
+      <c r="Z13" s="1"/>
+      <c r="AA13" s="7"/>
+      <c r="AB13" s="7"/>
+      <c r="AC13" s="7"/>
+      <c r="AD13" s="7"/>
+      <c r="AE13" s="7"/>
+      <c r="AF13" s="7"/>
+      <c r="AG13" s="7"/>
+      <c r="AH13" s="7"/>
+      <c r="AI13" s="7"/>
+      <c r="AJ13" s="7"/>
+      <c r="AK13" s="7"/>
+      <c r="AL13" s="7"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A14" s="5"/>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A14" s="13"/>
       <c r="B14" s="3" t="s">
         <v>27</v>
       </c>
@@ -1612,33 +2020,63 @@
       <c r="H14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="J14" s="16" t="s">
+      <c r="J14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K14" s="16" t="s">
+      <c r="K14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="L14" s="16" t="s">
+      <c r="L14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="M14" s="16" t="s">
+      <c r="M14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="N14" s="16" t="s">
+      <c r="N14" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="O14" s="16"/>
-      <c r="P14" s="16"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
+      <c r="O14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="R14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="S14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="T14" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="U14" s="1"/>
+      <c r="V14" s="1"/>
+      <c r="W14" s="1"/>
+      <c r="X14" s="1"/>
+      <c r="Y14" s="1"/>
+      <c r="Z14" s="1"/>
+      <c r="AA14" s="7"/>
+      <c r="AB14" s="7"/>
+      <c r="AC14" s="7"/>
+      <c r="AD14" s="7"/>
+      <c r="AE14" s="7"/>
+      <c r="AF14" s="7"/>
+      <c r="AG14" s="7"/>
+      <c r="AH14" s="7"/>
+      <c r="AI14" s="7"/>
+      <c r="AJ14" s="7"/>
+      <c r="AK14" s="7"/>
+      <c r="AL14" s="7"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A15" s="6"/>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A15" s="14"/>
       <c r="B15" s="3" t="s">
         <v>26</v>
       </c>
@@ -1660,83 +2098,143 @@
       <c r="H15" s="1">
         <v>10</v>
       </c>
-      <c r="I15" s="16">
+      <c r="I15" s="7">
         <v>5</v>
       </c>
-      <c r="J15" s="16">
+      <c r="J15" s="7">
         <v>5</v>
       </c>
-      <c r="K15" s="16">
+      <c r="K15" s="7">
         <v>5</v>
       </c>
-      <c r="L15" s="16">
+      <c r="L15" s="7">
         <v>5</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="7">
         <v>5</v>
       </c>
-      <c r="N15" s="16">
+      <c r="N15" s="7">
         <v>5</v>
       </c>
-      <c r="O15" s="16"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
+      <c r="O15" s="7">
+        <v>5</v>
+      </c>
+      <c r="P15" s="7">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="7">
+        <v>5</v>
+      </c>
+      <c r="R15" s="7">
+        <v>5</v>
+      </c>
+      <c r="S15" s="7">
+        <v>5</v>
+      </c>
+      <c r="T15" s="7">
+        <v>5</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1"/>
+      <c r="W15" s="1"/>
+      <c r="X15" s="1"/>
+      <c r="Y15" s="1"/>
+      <c r="Z15" s="1"/>
+      <c r="AA15" s="7"/>
+      <c r="AB15" s="7"/>
+      <c r="AC15" s="7"/>
+      <c r="AD15" s="7"/>
+      <c r="AE15" s="7"/>
+      <c r="AF15" s="7"/>
+      <c r="AG15" s="7"/>
+      <c r="AH15" s="7"/>
+      <c r="AI15" s="7"/>
+      <c r="AJ15" s="7"/>
+      <c r="AK15" s="7"/>
+      <c r="AL15" s="7"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="15" t="s">
+      <c r="C16" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="E16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="I16" s="16" t="s">
+      <c r="I16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J16" s="16" t="s">
+      <c r="J16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="K16" s="16" t="s">
+      <c r="K16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="L16" s="16" t="s">
+      <c r="L16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="N16" s="16" t="s">
+      <c r="N16" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="O16" s="16"/>
-      <c r="P16" s="16"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
+      <c r="O16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="R16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="S16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="T16" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="U16" s="5"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="7"/>
+      <c r="AB16" s="7"/>
+      <c r="AC16" s="7"/>
+      <c r="AD16" s="7"/>
+      <c r="AE16" s="7"/>
+      <c r="AF16" s="7"/>
+      <c r="AG16" s="7"/>
+      <c r="AH16" s="7"/>
+      <c r="AI16" s="7"/>
+      <c r="AJ16" s="7"/>
+      <c r="AK16" s="7"/>
+      <c r="AL16" s="7"/>
     </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A17" s="5"/>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A17" s="13"/>
       <c r="B17" s="3" t="s">
         <v>29</v>
       </c>
@@ -1776,15 +2274,45 @@
       <c r="N17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
+      <c r="O17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="R17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="S17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="T17" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="U17" s="1"/>
+      <c r="V17" s="1"/>
+      <c r="W17" s="1"/>
+      <c r="X17" s="1"/>
+      <c r="Y17" s="1"/>
+      <c r="Z17" s="1"/>
+      <c r="AA17" s="1"/>
+      <c r="AB17" s="1"/>
+      <c r="AC17" s="1"/>
+      <c r="AD17" s="1"/>
+      <c r="AE17" s="1"/>
+      <c r="AF17" s="1"/>
+      <c r="AG17" s="1"/>
+      <c r="AH17" s="1"/>
+      <c r="AI17" s="1"/>
+      <c r="AJ17" s="1"/>
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="1"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A18" s="5"/>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A18" s="13"/>
       <c r="B18" s="3" t="s">
         <v>19</v>
       </c>
@@ -1806,33 +2334,63 @@
       <c r="H18" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="5">
         <v>2</v>
       </c>
-      <c r="J18" s="14">
+      <c r="J18" s="5">
         <v>2</v>
       </c>
-      <c r="K18" s="14">
+      <c r="K18" s="5">
         <v>4</v>
       </c>
-      <c r="L18" s="14">
+      <c r="L18" s="5">
         <v>4</v>
       </c>
-      <c r="M18" s="14">
+      <c r="M18" s="5">
         <v>6</v>
       </c>
-      <c r="N18" s="14">
+      <c r="N18" s="5">
         <v>6</v>
       </c>
-      <c r="O18" s="14"/>
-      <c r="P18" s="14"/>
-      <c r="Q18" s="14"/>
-      <c r="R18" s="14"/>
-      <c r="S18" s="14"/>
-      <c r="T18" s="14"/>
+      <c r="O18" s="7">
+        <v>6</v>
+      </c>
+      <c r="P18" s="7">
+        <v>6</v>
+      </c>
+      <c r="Q18" s="7">
+        <v>6</v>
+      </c>
+      <c r="R18" s="7">
+        <v>6</v>
+      </c>
+      <c r="S18" s="7">
+        <v>6</v>
+      </c>
+      <c r="T18" s="7">
+        <v>6</v>
+      </c>
+      <c r="U18" s="1"/>
+      <c r="V18" s="1"/>
+      <c r="W18" s="1"/>
+      <c r="X18" s="1"/>
+      <c r="Y18" s="1"/>
+      <c r="Z18" s="1"/>
+      <c r="AA18" s="5"/>
+      <c r="AB18" s="5"/>
+      <c r="AC18" s="5"/>
+      <c r="AD18" s="5"/>
+      <c r="AE18" s="5"/>
+      <c r="AF18" s="5"/>
+      <c r="AG18" s="5"/>
+      <c r="AH18" s="5"/>
+      <c r="AI18" s="5"/>
+      <c r="AJ18" s="5"/>
+      <c r="AK18" s="5"/>
+      <c r="AL18" s="5"/>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A19" s="5"/>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A19" s="13"/>
       <c r="B19" s="3" t="s">
         <v>20</v>
       </c>
@@ -1872,15 +2430,45 @@
       <c r="N19" s="1">
         <v>100</v>
       </c>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
+      <c r="O19" s="1">
+        <v>100</v>
+      </c>
+      <c r="P19" s="1">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="1">
+        <v>100</v>
+      </c>
+      <c r="R19" s="1">
+        <v>100</v>
+      </c>
+      <c r="S19" s="1">
+        <v>100</v>
+      </c>
+      <c r="T19" s="1">
+        <v>100</v>
+      </c>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
+      <c r="W19" s="1"/>
+      <c r="X19" s="1"/>
+      <c r="Y19" s="1"/>
+      <c r="Z19" s="1"/>
+      <c r="AA19" s="1"/>
+      <c r="AB19" s="1"/>
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1"/>
+      <c r="AJ19" s="1"/>
+      <c r="AK19" s="1"/>
+      <c r="AL19" s="1"/>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A20" s="5"/>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A20" s="13"/>
       <c r="B20" s="3" t="s">
         <v>21</v>
       </c>
@@ -1920,15 +2508,45 @@
       <c r="N20" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1"/>
+      <c r="O20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
+      <c r="W20" s="1"/>
+      <c r="X20" s="1"/>
+      <c r="Y20" s="1"/>
+      <c r="Z20" s="1"/>
+      <c r="AA20" s="1"/>
+      <c r="AB20" s="1"/>
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+      <c r="AI20" s="1"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A21" s="6"/>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A21" s="14"/>
       <c r="B21" s="3" t="s">
         <v>22</v>
       </c>
@@ -1968,15 +2586,45 @@
       <c r="N21" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
+      <c r="O21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="T21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
+      <c r="W21" s="1"/>
+      <c r="X21" s="1"/>
+      <c r="Y21" s="1"/>
+      <c r="Z21" s="1"/>
+      <c r="AA21" s="1"/>
+      <c r="AB21" s="1"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+      <c r="AI21" s="1"/>
+      <c r="AJ21" s="1"/>
+      <c r="AK21" s="1"/>
+      <c r="AL21" s="1"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="3" t="s">
@@ -2018,15 +2666,45 @@
       <c r="N22" s="1">
         <v>200</v>
       </c>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1"/>
+      <c r="O22" s="1">
+        <v>200</v>
+      </c>
+      <c r="P22" s="1">
+        <v>200</v>
+      </c>
+      <c r="Q22" s="1">
+        <v>200</v>
+      </c>
+      <c r="R22" s="1">
+        <v>200</v>
+      </c>
+      <c r="S22" s="1">
+        <v>200</v>
+      </c>
+      <c r="T22" s="1">
+        <v>200</v>
+      </c>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
+      <c r="W22" s="1"/>
+      <c r="X22" s="1"/>
+      <c r="Y22" s="1"/>
+      <c r="Z22" s="1"/>
+      <c r="AA22" s="1"/>
+      <c r="AB22" s="1"/>
+      <c r="AC22" s="1"/>
+      <c r="AD22" s="1"/>
+      <c r="AE22" s="1"/>
+      <c r="AF22" s="1"/>
+      <c r="AG22" s="1"/>
+      <c r="AH22" s="1"/>
+      <c r="AI22" s="1"/>
+      <c r="AJ22" s="1"/>
+      <c r="AK22" s="1"/>
+      <c r="AL22" s="1"/>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A23" s="13"/>
       <c r="B23" s="3" t="s">
         <v>32</v>
       </c>
@@ -2066,15 +2744,45 @@
       <c r="N23" s="1">
         <v>32</v>
       </c>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
+      <c r="O23" s="1">
+        <v>32</v>
+      </c>
+      <c r="P23" s="1">
+        <v>32</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>32</v>
+      </c>
+      <c r="R23" s="1">
+        <v>32</v>
+      </c>
+      <c r="S23" s="1">
+        <v>32</v>
+      </c>
+      <c r="T23" s="1">
+        <v>32</v>
+      </c>
+      <c r="U23" s="1"/>
+      <c r="V23" s="1"/>
+      <c r="W23" s="1"/>
+      <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
+      <c r="Z23" s="1"/>
+      <c r="AA23" s="1"/>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1"/>
+      <c r="AF23" s="1"/>
+      <c r="AG23" s="1"/>
+      <c r="AH23" s="1"/>
+      <c r="AI23" s="1"/>
+      <c r="AJ23" s="1"/>
+      <c r="AK23" s="1"/>
+      <c r="AL23" s="1"/>
     </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A24" s="13"/>
       <c r="B24" s="3" t="s">
         <v>33</v>
       </c>
@@ -2114,15 +2822,45 @@
       <c r="N24" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
+      <c r="O24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="P24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="R24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="T24" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1"/>
+      <c r="X24" s="1"/>
+      <c r="Y24" s="1"/>
+      <c r="Z24" s="1"/>
+      <c r="AA24" s="1"/>
+      <c r="AB24" s="1"/>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="1"/>
     </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A25" s="6"/>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A25" s="14"/>
       <c r="B25" s="3" t="s">
         <v>34</v>
       </c>
@@ -2162,528 +2900,978 @@
       <c r="N25" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
+      <c r="O25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="P25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
+      <c r="AG25" s="1"/>
+      <c r="AH25" s="1"/>
+      <c r="AI25" s="1"/>
+      <c r="AJ25" s="1"/>
+      <c r="AK25" s="1"/>
+      <c r="AL25" s="1"/>
     </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="8">
         <v>0.27406494369061501</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="8">
         <v>0.28008107675005101</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="8">
         <v>0.37798544141750001</v>
       </c>
-      <c r="F26" s="17">
+      <c r="F26" s="8">
         <v>0.375604666527457</v>
       </c>
-      <c r="G26" s="17">
+      <c r="G26" s="8">
         <v>0.37316641645860699</v>
       </c>
-      <c r="H26" s="17">
+      <c r="H26" s="8">
         <v>7.2516807779941401E-7</v>
       </c>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
+      <c r="I26" s="8">
+        <v>1.87080658264051E-2</v>
+      </c>
+      <c r="J26" s="8">
+        <v>2.3326905239678598E-2</v>
+      </c>
+      <c r="K26" s="8">
+        <v>1.8328708976326599E-2</v>
+      </c>
+      <c r="L26" s="8">
+        <v>1.7881412241641002E-2</v>
+      </c>
+      <c r="M26" s="8">
+        <v>3.7472134596016601E-2</v>
+      </c>
+      <c r="N26" s="8">
+        <v>2.8661780070498199E-2</v>
+      </c>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
       <c r="T26" s="1"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="8"/>
+      <c r="Z26" s="8"/>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="1"/>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A27" s="5"/>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A27" s="13"/>
       <c r="B27" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="8">
         <v>0.27404304525080803</v>
       </c>
-      <c r="D27" s="17">
+      <c r="D27" s="8">
         <v>0.28879925652962901</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="8">
         <v>0.37851420019141302</v>
       </c>
-      <c r="F27" s="17">
+      <c r="F27" s="8">
         <v>0.37416380042209402</v>
       </c>
-      <c r="G27" s="17">
+      <c r="G27" s="8">
         <v>0.37312797441720003</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="8">
         <v>7.2570309588423802E-7</v>
       </c>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
+      <c r="I27" s="8">
+        <v>1.77922292155628E-2</v>
+      </c>
+      <c r="J27" s="8">
+        <v>2.26924086780112E-2</v>
+      </c>
+      <c r="K27" s="8">
+        <v>2.0370434033552199E-2</v>
+      </c>
+      <c r="L27" s="8">
+        <v>2.1088382117703801E-2</v>
+      </c>
+      <c r="M27" s="8">
+        <v>3.6112180946772002E-2</v>
+      </c>
+      <c r="N27" s="8">
+        <v>3.6551786930307098E-2</v>
+      </c>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
       <c r="T27" s="1"/>
+      <c r="U27" s="8"/>
+      <c r="V27" s="8"/>
+      <c r="W27" s="8"/>
+      <c r="X27" s="8"/>
+      <c r="Y27" s="8"/>
+      <c r="Z27" s="8"/>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="1"/>
+      <c r="AI27" s="1"/>
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="1"/>
+      <c r="AL27" s="1"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A28" s="5"/>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A28" s="13"/>
       <c r="B28" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="8">
         <v>3.2078614771898899E-4</v>
       </c>
-      <c r="D28" s="17">
+      <c r="D28" s="8">
         <v>2.2279385236569998E-2</v>
       </c>
-      <c r="E28" s="17">
+      <c r="E28" s="8">
         <v>5.5896811402404703E-3</v>
       </c>
-      <c r="F28" s="17">
+      <c r="F28" s="8">
         <v>6.2732577810948502E-3</v>
       </c>
-      <c r="G28" s="17">
+      <c r="G28" s="8">
         <v>5.1182400108654496E-3</v>
       </c>
-      <c r="H28" s="17">
+      <c r="H28" s="8">
         <v>1.39338410894414E-8</v>
       </c>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
+      <c r="I28" s="8">
+        <v>3.9427745384379804E-3</v>
+      </c>
+      <c r="J28" s="8">
+        <v>7.4589192580138E-3</v>
+      </c>
+      <c r="K28" s="8">
+        <v>9.2881353665945007E-3</v>
+      </c>
+      <c r="L28" s="8">
+        <v>1.00325278958744E-2</v>
+      </c>
+      <c r="M28" s="8">
+        <v>1.37502784003838E-2</v>
+      </c>
+      <c r="N28" s="8">
+        <v>1.30252519027582E-2</v>
+      </c>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
       <c r="S28" s="1"/>
       <c r="T28" s="1"/>
+      <c r="U28" s="8"/>
+      <c r="V28" s="8"/>
+      <c r="W28" s="8"/>
+      <c r="X28" s="8"/>
+      <c r="Y28" s="8"/>
+      <c r="Z28" s="8"/>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
+      <c r="AI28" s="1"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="1"/>
+      <c r="AL28" s="1"/>
     </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A29" s="5"/>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A29" s="13"/>
       <c r="B29" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="8">
         <v>1.3765970268683001</v>
       </c>
-      <c r="D29" s="17">
+      <c r="D29" s="8">
         <v>1.49536228991653</v>
       </c>
-      <c r="E29" s="17">
+      <c r="E29" s="8">
         <v>6.4896047158645302</v>
       </c>
-      <c r="F29" s="17">
+      <c r="F29" s="8">
         <v>6.0037061517075196</v>
       </c>
-      <c r="G29" s="17">
+      <c r="G29" s="8">
         <v>6.3133028085217502</v>
       </c>
-      <c r="H29" s="17">
+      <c r="H29" s="8">
         <v>1.98246004799313E-5</v>
       </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
+      <c r="I29" s="8">
+        <v>0.345481649843422</v>
+      </c>
+      <c r="J29" s="8">
+        <v>0.48665578900380202</v>
+      </c>
+      <c r="K29" s="8">
+        <v>0.25995857577744502</v>
+      </c>
+      <c r="L29" s="8">
+        <v>0.23485783799196999</v>
+      </c>
+      <c r="M29" s="8">
+        <v>0.41457133330232998</v>
+      </c>
+      <c r="N29" s="8">
+        <v>0.53596136859992205</v>
+      </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1"/>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
       <c r="S29" s="1"/>
       <c r="T29" s="1"/>
+      <c r="U29" s="8"/>
+      <c r="V29" s="8"/>
+      <c r="W29" s="8"/>
+      <c r="X29" s="8"/>
+      <c r="Y29" s="8"/>
+      <c r="Z29" s="8"/>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1"/>
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
+      <c r="AL29" s="1"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A30" s="13"/>
       <c r="B30" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="8">
         <v>1.4950867994121899</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="8">
         <v>1.6825509519204001</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="8">
         <v>7.0971543017818401</v>
       </c>
-      <c r="F30" s="17">
+      <c r="F30" s="8">
         <v>6.9781572970058496</v>
       </c>
-      <c r="G30" s="17">
+      <c r="G30" s="8">
         <v>6.9735315950655004</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="8">
         <v>2.4089279700452699E-5</v>
       </c>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
+      <c r="I30" s="8">
+        <v>0.41689717218268701</v>
+      </c>
+      <c r="J30" s="8">
+        <v>0.56586691463163796</v>
+      </c>
+      <c r="K30" s="8">
+        <v>0.39802814710809797</v>
+      </c>
+      <c r="L30" s="8">
+        <v>0.25503487708558797</v>
+      </c>
+      <c r="M30" s="8">
+        <v>0.52400765112105596</v>
+      </c>
+      <c r="N30" s="8">
+        <v>0.45267229526063602</v>
+      </c>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
       <c r="S30" s="1"/>
       <c r="T30" s="1"/>
+      <c r="U30" s="8"/>
+      <c r="V30" s="8"/>
+      <c r="W30" s="8"/>
+      <c r="X30" s="8"/>
+      <c r="Y30" s="8"/>
+      <c r="Z30" s="8"/>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+      <c r="AG30" s="1"/>
+      <c r="AH30" s="1"/>
+      <c r="AI30" s="1"/>
+      <c r="AJ30" s="1"/>
+      <c r="AK30" s="1"/>
+      <c r="AL30" s="1"/>
     </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A31" s="6"/>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A31" s="14"/>
       <c r="B31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="8">
         <v>0.30723732832767398</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="8">
         <v>0.411111128807233</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="8">
         <v>2.57910424814825</v>
       </c>
-      <c r="F31" s="17">
+      <c r="F31" s="8">
         <v>2.6663375305093902</v>
       </c>
-      <c r="G31" s="17">
+      <c r="G31" s="8">
         <v>2.7083599982556299</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="8">
         <v>1.36211644979319E-5</v>
       </c>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
+      <c r="I31" s="8">
+        <v>0.112644484096489</v>
+      </c>
+      <c r="J31" s="8">
+        <v>0.22041776512389399</v>
+      </c>
+      <c r="K31" s="8">
+        <v>0.29327572382023698</v>
+      </c>
+      <c r="L31" s="8">
+        <v>9.2875983714764396E-2</v>
+      </c>
+      <c r="M31" s="8">
+        <v>0.30141032466172801</v>
+      </c>
+      <c r="N31" s="8">
+        <v>0.127039325398561</v>
+      </c>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
       <c r="R31" s="1"/>
       <c r="S31" s="1"/>
       <c r="T31" s="1"/>
+      <c r="U31" s="8"/>
+      <c r="V31" s="8"/>
+      <c r="W31" s="8"/>
+      <c r="X31" s="8"/>
+      <c r="Y31" s="8"/>
+      <c r="Z31" s="8"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AI31" s="1"/>
+      <c r="AJ31" s="1"/>
+      <c r="AK31" s="1"/>
+      <c r="AL31" s="1"/>
     </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
         <v>16</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="17">
+      <c r="C32" s="8">
         <v>0.25452937173933998</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="8">
         <v>0.262636202101523</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="8">
         <v>0.36457363153411199</v>
       </c>
-      <c r="F32" s="17">
+      <c r="F32" s="8">
         <v>0.35826598368370799</v>
       </c>
-      <c r="G32" s="17">
+      <c r="G32" s="8">
         <v>0.357390215620076</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="8">
         <v>1.17705754203105E-2</v>
       </c>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
+      <c r="I32" s="8">
+        <v>3.3545351815201199E-2</v>
+      </c>
+      <c r="J32" s="8">
+        <v>5.0781163191583503E-2</v>
+      </c>
+      <c r="K32" s="8">
+        <v>3.1830252801525703E-2</v>
+      </c>
+      <c r="L32" s="8">
+        <v>4.5722906216159702E-2</v>
+      </c>
+      <c r="M32" s="8">
+        <v>4.8557273452136902E-2</v>
+      </c>
+      <c r="N32" s="8">
+        <v>4.6853662767427799E-2</v>
+      </c>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
       <c r="S32" s="1"/>
       <c r="T32" s="1"/>
+      <c r="U32" s="8"/>
+      <c r="V32" s="8"/>
+      <c r="W32" s="8"/>
+      <c r="X32" s="8"/>
+      <c r="Y32" s="8"/>
+      <c r="Z32" s="8"/>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1"/>
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
     </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A33" s="5"/>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A33" s="13"/>
       <c r="B33" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C33" s="17">
+      <c r="C33" s="8">
         <v>0.254479752907593</v>
       </c>
-      <c r="D33" s="17">
+      <c r="D33" s="8">
         <v>0.26496203453061401</v>
       </c>
-      <c r="E33" s="17">
+      <c r="E33" s="8">
         <v>0.36554365585384302</v>
       </c>
-      <c r="F33" s="17">
+      <c r="F33" s="8">
         <v>0.35803513346293098</v>
       </c>
-      <c r="G33" s="17">
+      <c r="G33" s="8">
         <v>0.35738965802700401</v>
       </c>
-      <c r="H33" s="17">
+      <c r="H33" s="8">
         <v>1.1826512653510099E-2</v>
       </c>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
+      <c r="I33" s="8">
+        <v>3.3880117711883803E-2</v>
+      </c>
+      <c r="J33" s="8">
+        <v>4.9099438479382598E-2</v>
+      </c>
+      <c r="K33" s="8">
+        <v>3.4151916279849898E-2</v>
+      </c>
+      <c r="L33" s="8">
+        <v>4.5661336045176297E-2</v>
+      </c>
+      <c r="M33" s="8">
+        <v>4.7477527629746101E-2</v>
+      </c>
+      <c r="N33" s="8">
+        <v>5.0359656653457797E-2</v>
+      </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
       <c r="S33" s="1"/>
       <c r="T33" s="1"/>
+      <c r="U33" s="8"/>
+      <c r="V33" s="8"/>
+      <c r="W33" s="8"/>
+      <c r="X33" s="8"/>
+      <c r="Y33" s="8"/>
+      <c r="Z33" s="8"/>
+      <c r="AA33" s="1"/>
+      <c r="AB33" s="1"/>
+      <c r="AC33" s="1"/>
+      <c r="AD33" s="1"/>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AI33" s="1"/>
+      <c r="AJ33" s="1"/>
+      <c r="AK33" s="1"/>
+      <c r="AL33" s="1"/>
     </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A34" s="5"/>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A34" s="13"/>
       <c r="B34" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="C34" s="17">
+      <c r="C34" s="8">
         <v>6.1188120723027395E-4</v>
       </c>
-      <c r="D34" s="17">
+      <c r="D34" s="8">
         <v>6.2977673898870698E-3</v>
       </c>
-      <c r="E34" s="17">
+      <c r="E34" s="8">
         <v>7.2952730996060098E-3</v>
       </c>
-      <c r="F34" s="17">
+      <c r="F34" s="8">
         <v>6.4238730604032597E-3</v>
       </c>
-      <c r="G34" s="17">
+      <c r="G34" s="8">
         <v>6.1464722135944998E-3</v>
       </c>
-      <c r="H34" s="17">
+      <c r="H34" s="8">
         <v>9.6320799193618596E-4</v>
       </c>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
+      <c r="I34" s="8">
+        <v>2.8253201012084801E-3</v>
+      </c>
+      <c r="J34" s="8">
+        <v>3.2205761743692102E-3</v>
+      </c>
+      <c r="K34" s="8">
+        <v>7.29421158677149E-3</v>
+      </c>
+      <c r="L34" s="8">
+        <v>9.6806277925442499E-4</v>
+      </c>
+      <c r="M34" s="8">
+        <v>1.06340718142462E-2</v>
+      </c>
+      <c r="N34" s="8">
+        <v>7.12342650262695E-3</v>
+      </c>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
+      <c r="U34" s="8"/>
+      <c r="V34" s="8"/>
+      <c r="W34" s="8"/>
+      <c r="X34" s="8"/>
+      <c r="Y34" s="8"/>
+      <c r="Z34" s="8"/>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+      <c r="AI34" s="1"/>
+      <c r="AJ34" s="1"/>
+      <c r="AK34" s="1"/>
+      <c r="AL34" s="1"/>
     </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A35" s="5"/>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A35" s="13"/>
       <c r="B35" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C35" s="17">
+      <c r="C35" s="8">
         <v>1.34087368521262</v>
       </c>
-      <c r="D35" s="17">
+      <c r="D35" s="8">
         <v>1.49372888280297</v>
       </c>
-      <c r="E35" s="17">
+      <c r="E35" s="8">
         <v>5.5755228975029896</v>
       </c>
-      <c r="F35" s="17">
+      <c r="F35" s="8">
         <v>5.2290905297135701</v>
       </c>
-      <c r="G35" s="17">
+      <c r="G35" s="8">
         <v>5.1576745064626603</v>
       </c>
-      <c r="H35" s="17">
+      <c r="H35" s="8">
         <v>0.23098580506170799</v>
       </c>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
+      <c r="I35" s="8">
+        <v>0.405474622377962</v>
+      </c>
+      <c r="J35" s="8">
+        <v>1.6311922737873901</v>
+      </c>
+      <c r="K35" s="8">
+        <v>0.55542981317712004</v>
+      </c>
+      <c r="L35" s="8">
+        <v>0.659986616753507</v>
+      </c>
+      <c r="M35" s="8">
+        <v>0.71311916033877298</v>
+      </c>
+      <c r="N35" s="8">
+        <v>0.70378627426210605</v>
+      </c>
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
       <c r="S35" s="1"/>
       <c r="T35" s="1"/>
+      <c r="U35" s="8"/>
+      <c r="V35" s="8"/>
+      <c r="W35" s="8"/>
+      <c r="X35" s="8"/>
+      <c r="Y35" s="8"/>
+      <c r="Z35" s="8"/>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+      <c r="AG35" s="1"/>
+      <c r="AH35" s="1"/>
+      <c r="AI35" s="1"/>
+      <c r="AJ35" s="1"/>
+      <c r="AK35" s="1"/>
+      <c r="AL35" s="1"/>
     </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A36" s="5"/>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A36" s="13"/>
       <c r="B36" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="17">
+      <c r="C36" s="8">
         <v>2.0150733074749398</v>
       </c>
-      <c r="D36" s="17">
+      <c r="D36" s="8">
         <v>2.0535243821834301</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="8">
         <v>8.7603068378516795</v>
       </c>
-      <c r="F36" s="17">
+      <c r="F36" s="8">
         <v>8.0956815576086996</v>
       </c>
-      <c r="G36" s="17">
+      <c r="G36" s="8">
         <v>7.4242067738040696</v>
       </c>
-      <c r="H36" s="17">
+      <c r="H36" s="8">
         <v>0.54659137185518603</v>
       </c>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
+      <c r="I36" s="8">
+        <v>0.63253032842198598</v>
+      </c>
+      <c r="J36" s="8">
+        <v>1.3812367693490499</v>
+      </c>
+      <c r="K36" s="8">
+        <v>0.53076092711970801</v>
+      </c>
+      <c r="L36" s="8">
+        <v>1.02791767026462</v>
+      </c>
+      <c r="M36" s="8">
+        <v>0.67111044507009499</v>
+      </c>
+      <c r="N36" s="8">
+        <v>0.789670524432451</v>
+      </c>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
       <c r="S36" s="1"/>
       <c r="T36" s="1"/>
+      <c r="U36" s="8"/>
+      <c r="V36" s="8"/>
+      <c r="W36" s="8"/>
+      <c r="X36" s="8"/>
+      <c r="Y36" s="8"/>
+      <c r="Z36" s="8"/>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1"/>
+      <c r="AH36" s="1"/>
+      <c r="AI36" s="1"/>
+      <c r="AJ36" s="1"/>
+      <c r="AK36" s="1"/>
+      <c r="AL36" s="1"/>
     </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A37" s="6"/>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A37" s="14"/>
       <c r="B37" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C37" s="17">
+      <c r="C37" s="8">
         <v>1.61521140783543</v>
       </c>
-      <c r="D37" s="17">
+      <c r="D37" s="8">
         <v>1.1777564177884099</v>
       </c>
-      <c r="E37" s="17">
+      <c r="E37" s="8">
         <v>8.4735409790791003</v>
       </c>
-      <c r="F37" s="17">
+      <c r="F37" s="8">
         <v>6.9873755204774097</v>
       </c>
-      <c r="G37" s="17">
+      <c r="G37" s="8">
         <v>5.6561705502603701</v>
       </c>
-      <c r="H37" s="17">
+      <c r="H37" s="8">
         <v>0.70760953078840805</v>
       </c>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
+      <c r="I37" s="8">
+        <v>0.36074744699437999</v>
+      </c>
+      <c r="J37" s="8">
+        <v>0.47574322330603003</v>
+      </c>
+      <c r="K37" s="8">
+        <v>0.152563583058172</v>
+      </c>
+      <c r="L37" s="8">
+        <v>0.62949559624055795</v>
+      </c>
+      <c r="M37" s="8">
+        <v>0.20257342745964299</v>
+      </c>
+      <c r="N37" s="8">
+        <v>0.33990499807753199</v>
+      </c>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
       <c r="S37" s="1"/>
       <c r="T37" s="1"/>
+      <c r="U37" s="8"/>
+      <c r="V37" s="8"/>
+      <c r="W37" s="8"/>
+      <c r="X37" s="8"/>
+      <c r="Y37" s="8"/>
+      <c r="Z37" s="8"/>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+      <c r="AG37" s="1"/>
+      <c r="AH37" s="1"/>
+      <c r="AI37" s="1"/>
+      <c r="AJ37" s="1"/>
+      <c r="AK37" s="1"/>
+      <c r="AL37" s="1"/>
     </row>
-    <row r="38" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A38" s="4" t="s">
+    <row r="38" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I38" s="8">
+        <v>8.5889625549316406</v>
+      </c>
+      <c r="J38" s="8">
+        <v>10.3243660926818</v>
+      </c>
+      <c r="K38" s="8">
+        <v>9.8971140384674001</v>
+      </c>
+      <c r="L38" s="8">
+        <v>11.690249204635601</v>
+      </c>
+      <c r="M38" s="8">
+        <v>11.699301958084099</v>
+      </c>
+      <c r="N38" s="8">
+        <v>13.859990119934</v>
+      </c>
+      <c r="O38" s="7"/>
+      <c r="P38" s="7"/>
+      <c r="Q38" s="7"/>
+      <c r="R38" s="7"/>
+      <c r="S38" s="7"/>
+      <c r="T38" s="7"/>
+      <c r="U38" s="1"/>
+      <c r="V38" s="1"/>
+      <c r="W38" s="1"/>
+      <c r="X38" s="1"/>
+      <c r="Y38" s="1"/>
+      <c r="Z38" s="1"/>
+      <c r="AA38" s="7"/>
+      <c r="AB38" s="7"/>
+      <c r="AC38" s="7"/>
+      <c r="AD38" s="7"/>
+      <c r="AE38" s="7"/>
+      <c r="AF38" s="7"/>
+      <c r="AG38" s="7"/>
+      <c r="AH38" s="7"/>
+      <c r="AI38" s="7"/>
+      <c r="AJ38" s="7"/>
+      <c r="AK38" s="7"/>
+      <c r="AL38" s="7"/>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A39" s="13"/>
+      <c r="B39" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="C39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I39" s="8">
+        <v>8.6415173053741405</v>
+      </c>
+      <c r="J39" s="8">
+        <v>10.353552865982</v>
+      </c>
+      <c r="K39" s="8">
+        <v>9.9057080745697004</v>
+      </c>
+      <c r="L39" s="8">
+        <v>11.894684648513699</v>
+      </c>
+      <c r="M39" s="8">
+        <v>11.7004350185394</v>
+      </c>
+      <c r="N39" s="8">
+        <v>13.750060606002799</v>
+      </c>
+      <c r="O39" s="7"/>
+      <c r="P39" s="7"/>
+      <c r="Q39" s="7"/>
+      <c r="R39" s="7"/>
+      <c r="S39" s="7"/>
+      <c r="T39" s="7"/>
+      <c r="U39" s="1"/>
+      <c r="V39" s="1"/>
+      <c r="W39" s="1"/>
+      <c r="X39" s="1"/>
+      <c r="Y39" s="1"/>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="7"/>
+      <c r="AB39" s="7"/>
+      <c r="AC39" s="7"/>
+      <c r="AD39" s="7"/>
+      <c r="AE39" s="7"/>
+      <c r="AF39" s="7"/>
+      <c r="AG39" s="7"/>
+      <c r="AH39" s="7"/>
+      <c r="AI39" s="7"/>
+      <c r="AJ39" s="7"/>
+      <c r="AK39" s="7"/>
+      <c r="AL39" s="7"/>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.3">
+      <c r="A40" s="14"/>
+      <c r="B40" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-      <c r="K38" s="16"/>
-      <c r="L38" s="16"/>
-      <c r="M38" s="16"/>
-      <c r="N38" s="16"/>
-      <c r="O38" s="16"/>
-      <c r="P38" s="16"/>
-      <c r="Q38" s="16"/>
-      <c r="R38" s="16"/>
-      <c r="S38" s="16"/>
-      <c r="T38" s="16"/>
-    </row>
-    <row r="39" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A39" s="5"/>
-      <c r="B39" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-      <c r="K39" s="16"/>
-      <c r="L39" s="16"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
-      <c r="O39" s="16"/>
-      <c r="P39" s="16"/>
-      <c r="Q39" s="16"/>
-      <c r="R39" s="16"/>
-      <c r="S39" s="16"/>
-      <c r="T39" s="16"/>
-    </row>
-    <row r="40" spans="1:20" x14ac:dyDescent="0.3">
-      <c r="A40" s="6"/>
-      <c r="B40" s="3" t="s">
-        <v>73</v>
-      </c>
       <c r="C40" s="1" t="s">
         <v>38</v>
       </c>
@@ -2702,26 +3890,64 @@
       <c r="H40" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
+      <c r="I40" s="8">
+        <v>0.14958733186982501</v>
+      </c>
+      <c r="J40" s="8">
+        <v>0.23023710744799</v>
+      </c>
+      <c r="K40" s="8">
+        <v>0.20138440547373501</v>
+      </c>
+      <c r="L40" s="8">
+        <v>0.54840962182135</v>
+      </c>
+      <c r="M40" s="8">
+        <v>0.14503784019133001</v>
+      </c>
+      <c r="N40" s="8">
+        <v>0.251512352315993</v>
+      </c>
+      <c r="O40" s="7"/>
+      <c r="P40" s="7"/>
+      <c r="Q40" s="7"/>
+      <c r="R40" s="7"/>
+      <c r="S40" s="7"/>
+      <c r="T40" s="7"/>
+      <c r="U40" s="1"/>
+      <c r="V40" s="1"/>
+      <c r="W40" s="1"/>
+      <c r="X40" s="1"/>
+      <c r="Y40" s="1"/>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="7"/>
+      <c r="AB40" s="7"/>
+      <c r="AC40" s="7"/>
+      <c r="AD40" s="7"/>
+      <c r="AE40" s="7"/>
+      <c r="AF40" s="7"/>
+      <c r="AG40" s="7"/>
+      <c r="AH40" s="7"/>
+      <c r="AI40" s="7"/>
+      <c r="AJ40" s="7"/>
+      <c r="AK40" s="7"/>
+      <c r="AL40" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="O2:T2"/>
-    <mergeCell ref="O3:T3"/>
-    <mergeCell ref="O4:T4"/>
-    <mergeCell ref="O5:T5"/>
-    <mergeCell ref="A38:A40"/>
+  <mergeCells count="35">
+    <mergeCell ref="U4:Z4"/>
+    <mergeCell ref="AA4:AF4"/>
+    <mergeCell ref="AG4:AL4"/>
+    <mergeCell ref="U5:Z5"/>
+    <mergeCell ref="AA5:AF5"/>
+    <mergeCell ref="AG5:AL5"/>
+    <mergeCell ref="U1:AL1"/>
+    <mergeCell ref="U2:Z2"/>
+    <mergeCell ref="AA2:AF2"/>
+    <mergeCell ref="AG2:AL2"/>
+    <mergeCell ref="U3:Z3"/>
+    <mergeCell ref="AA3:AF3"/>
+    <mergeCell ref="AG3:AL3"/>
     <mergeCell ref="C1:T1"/>
     <mergeCell ref="I2:N2"/>
     <mergeCell ref="I5:N5"/>
@@ -2730,15 +3956,20 @@
     <mergeCell ref="I3:N3"/>
     <mergeCell ref="C4:H4"/>
     <mergeCell ref="I4:N4"/>
-    <mergeCell ref="A22:A25"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="C5:H5"/>
     <mergeCell ref="C2:H2"/>
     <mergeCell ref="A1:A5"/>
     <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="O2:T2"/>
+    <mergeCell ref="O3:T3"/>
+    <mergeCell ref="O4:T4"/>
+    <mergeCell ref="O5:T5"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A22:A25"/>
     <mergeCell ref="A32:A37"/>
     <mergeCell ref="A26:A31"/>
-    <mergeCell ref="A10:A12"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
